--- a/links/Juegos_PS2.xlsx
+++ b/links/Juegos_PS2.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -417,18 +417,6 @@
     <col min="16" max="16" width="35.83203125" customWidth="1"/>
     <col min="17" max="17" width="35.83203125" customWidth="1"/>
     <col min="18" max="18" width="35.83203125" customWidth="1"/>
-    <col min="19" max="19" width="35.83203125" customWidth="1"/>
-    <col min="20" max="20" width="35.83203125" customWidth="1"/>
-    <col min="21" max="21" width="35.83203125" customWidth="1"/>
-    <col min="22" max="22" width="35.83203125" customWidth="1"/>
-    <col min="23" max="23" width="35.83203125" customWidth="1"/>
-    <col min="24" max="24" width="35.83203125" customWidth="1"/>
-    <col min="25" max="25" width="35.83203125" customWidth="1"/>
-    <col min="26" max="26" width="35.83203125" customWidth="1"/>
-    <col min="27" max="27" width="35.83203125" customWidth="1"/>
-    <col min="28" max="28" width="35.83203125" customWidth="1"/>
-    <col min="29" max="29" width="35.83203125" customWidth="1"/>
-    <col min="30" max="30" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,81 +433,45 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
-        <v>Mega Parte 1</v>
-      </c>
       <c r="H1" t="str">
-        <v>Mega Parte 2</v>
+        <v>Mediafire</v>
       </c>
       <c r="I1" t="str">
-        <v>Mega Parte 3</v>
+        <v>1Fichier</v>
       </c>
       <c r="J1" t="str">
-        <v>Mega Parte 4</v>
+        <v>Google Drive</v>
       </c>
       <c r="K1" t="str">
-        <v>Mediafire</v>
+        <v>Qiwi</v>
       </c>
       <c r="L1" t="str">
-        <v>Mediafire Parte 1</v>
+        <v>Pixeldrain</v>
       </c>
       <c r="M1" t="str">
-        <v>Mediafire Parte 2</v>
+        <v>Megaup</v>
       </c>
       <c r="N1" t="str">
-        <v>Mediafire Parte 3</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="O1" t="str">
-        <v>1Fichier</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="P1" t="str">
-        <v>1Fichier Parte 1</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="Q1" t="str">
-        <v>1Fichier Parte 2</v>
+        <v>Otro Link 4</v>
       </c>
       <c r="R1" t="str">
-        <v>Google Drive</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Google Drive Parte 1</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Google Drive Parte 2</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Google Drive Parte 3</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Google Drive Parte 4</v>
-      </c>
-      <c r="W1" t="str">
-        <v>Qiwi</v>
-      </c>
-      <c r="X1" t="str">
-        <v>Pixeldrain</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>Megaup</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Otro Link 1</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>Otro Link 4</v>
-      </c>
-      <c r="AD1" t="str">
         <v>Otro Link 5</v>
       </c>
     </row>
@@ -537,42 +489,21 @@
         <v>imagenes/PS2/Virtual View Nemoto Harumi Eyes Play.jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
-      </c>
-      <c r="G2" t="str">
-        <v>https://mega.nz/#!TZxBgTYC!R9PwnoMNZwTMjAabtztxyOV39cD9BMEBsSNK-lWCS74</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
       </c>
       <c r="H2" t="str">
-        <v>https://mega.nz/#!DZQ3FIYB!gKOyu1RqdpIK-_wlvdXFT6PlHo4OD_Y6eNI73X6mtdk</v>
-      </c>
-      <c r="I2" t="str">
-        <v>https://mega.nz/#!3RQ1zKhA!o928Kpfh2tNQQVXw5UYyvHZ_DK1Yc4OEN0PFnuGIhAs</v>
-      </c>
-      <c r="J2" t="str">
-        <v>https://mega.nz/#!7VZkxQoK!GAKJPDiy5el7d0I5NmxukuOc-y6LrGosMhUzciyWnBA</v>
-      </c>
-      <c r="K2" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="S2" t="str">
-        <v>https://drive.google.com/open?id=1IxEm8GvwkfvnKr9ucPdqIBlwa3A99RMo</v>
-      </c>
-      <c r="T2" t="str">
-        <v>https://drive.google.com/open?id=1c_B3sKJv4meSkQgET1eOdE5hBPlX9bCJ</v>
-      </c>
-      <c r="U2" t="str">
-        <v>https://drive.google.com/open?id=1QfrAyhBYTlFE3IbgrCunEKSn1rkI3atr</v>
-      </c>
-      <c r="V2" t="str">
-        <v>https://drive.google.com/open?id=1wKCzf5oBcHXD1-4LiGmFzbf6P8HVN6wY</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB2" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N2" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O2" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P2" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -590,21 +521,24 @@
         <v>imagenes/PS2/Motion Gravure Series Megumi.jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
-      </c>
-      <c r="K3" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="Z3" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="H3" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N3" t="str">
         <v>https://filecrypt.cc/Container/B1F9717E66.html</v>
       </c>
-      <c r="AA3" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC3" t="str">
+      <c r="O3" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P3" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q3" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -622,21 +556,24 @@
         <v>imagenes/PS2/The Battle of Yuu Yuu Hakusho Shitou Ankoku Bujuts.jpg</v>
       </c>
       <c r="E4" t="str">
-        <v>No</v>
-      </c>
-      <c r="K4" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="Z4" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F4" t="str">
+        <v>No</v>
+      </c>
+      <c r="H4" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N4" t="str">
         <v>https://downloadgameps3.net/archives/13881</v>
       </c>
-      <c r="AA4" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC4" t="str">
+      <c r="O4" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P4" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q4" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -654,24 +591,21 @@
         <v>imagenes/PS2/Motion Gravure Series Mori Hiroko.jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F5" t="str">
+        <v>No</v>
+      </c>
+      <c r="G5" t="str">
         <v>https://mega.nz/#!PH53gQyL!t3IvFTomi-jUgW3cuIVF-LYgGBEDP0uWpc_1c-HjRf4</v>
       </c>
-      <c r="L5" t="str">
-        <v>http://www.mediafire.com/file/3c2ez8g74yg9m5a/Motion_Gravure_Series_Mori_Hiroko_%255BNTSC-J%255D.rar/file</v>
-      </c>
-      <c r="M5" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB5" t="str">
+      <c r="N5" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O5" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P5" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -689,24 +623,21 @@
         <v>imagenes/PS2/Motion Gravure Series Nemoto Harumi.jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="G6" t="str">
         <v>https://mega.nz/#!aO4y3AoL!2VhUhiyov4CNSKLeyIQtFg1K7H7ReIEwTUXb0XkqyQw</v>
       </c>
-      <c r="L6" t="str">
-        <v>http://www.mediafire.com/file/9zf04i52ds7hskd/Motion_Gravure_Series_Nemoto_Harumi_%5BNTSC-J%5D.rar</v>
-      </c>
-      <c r="M6" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="Z6" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA6" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB6" t="str">
+      <c r="N6" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O6" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P6" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -724,24 +655,27 @@
         <v>imagenes/PS2/Street Fighter 3 3rd Strike Fight For The Future.jpg</v>
       </c>
       <c r="E7" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F7" t="str">
+        <v>No</v>
+      </c>
+      <c r="G7" t="str">
         <v>https://mega.nz/#!LipkCYiB!3qXRKh2Htuh7b2UIDfFVG4IVGJ_1K6GUnq1SwMkKduk</v>
       </c>
-      <c r="K7" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      <c r="H7" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I7" t="str">
+        <v>https://1fichier.com/?g0te0ps5sz</v>
+      </c>
+      <c r="N7" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O7" t="str">
-        <v>https://1fichier.com/?g0te0ps5sz</v>
-      </c>
-      <c r="Z7" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB7" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P7" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -759,27 +693,24 @@
         <v>imagenes/PS2/MAR Heaven ARM Fight Dream.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="G8" t="str">
         <v>https://mega.nz/#!s6RgCLwa!rVFYF9CzU7xYUhTAfaAmSGCpjrq57G2lNtPVP0dHk6M</v>
       </c>
-      <c r="L8" t="str">
-        <v>http://www.mediafire.com/file/4wfmsafc4axd6vl/Marheaven_Arm_Fight_Dream_%255BNTSC-J%255D.rar/file</v>
-      </c>
-      <c r="M8" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      <c r="I8" t="str">
+        <v>https://1fichier.com/?xsiohsllcj</v>
+      </c>
+      <c r="N8" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O8" t="str">
-        <v>https://1fichier.com/?xsiohsllcj</v>
-      </c>
-      <c r="Z8" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB8" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P8" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -797,21 +728,24 @@
         <v>imagenes/PS2/Kinnikuman Muscle Grand Prix Max.jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
-      </c>
-      <c r="K9" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="H9" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I9" t="str">
+        <v>https://1fichier.com/?p6e6rlg9qg</v>
+      </c>
+      <c r="N9" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O9" t="str">
-        <v>https://1fichier.com/?p6e6rlg9qg</v>
-      </c>
-      <c r="Z9" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA9" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB9" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P9" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -829,24 +763,27 @@
         <v>imagenes/PS2/Battle Stadium DON.jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="K10" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
+      </c>
+      <c r="H10" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I10" t="str">
+        <v>https://1fichier.com/?67gsvvim9t</v>
+      </c>
+      <c r="N10" t="str">
+        <v>https://downloadgameps3.net/archives/13879</v>
       </c>
       <c r="O10" t="str">
-        <v>https://1fichier.com/?67gsvvim9t</v>
-      </c>
-      <c r="Z10" t="str">
-        <v>https://downloadgameps3.net/archives/13879</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB10" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC10" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P10" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q10" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -864,24 +801,27 @@
         <v>imagenes/PS2/Pro Evolution Soccer 2014 [PES 2014].jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="K11" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
+      </c>
+      <c r="H11" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I11" t="str">
+        <v>https://1fichier.com/?2xaudnjqcb</v>
+      </c>
+      <c r="N11" t="str">
+        <v>https://letsupload.io/48Bmf</v>
       </c>
       <c r="O11" t="str">
-        <v>https://1fichier.com/?2xaudnjqcb</v>
-      </c>
-      <c r="Z11" t="str">
-        <v>https://letsupload.io/48Bmf</v>
-      </c>
-      <c r="AA11" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB11" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC11" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P11" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q11" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -899,27 +839,30 @@
         <v>imagenes/PS2/FIFA 14.jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
-      </c>
-      <c r="K12" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F12" t="str">
+        <v>No</v>
+      </c>
+      <c r="H12" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I12" t="str">
+        <v>https://1fichier.com/?9hjrqv8k9a</v>
+      </c>
+      <c r="N12" t="str">
+        <v>https://downloadgameps3.net/archives/16066</v>
       </c>
       <c r="O12" t="str">
-        <v>https://1fichier.com/?9hjrqv8k9a</v>
-      </c>
-      <c r="Z12" t="str">
-        <v>https://downloadgameps3.net/archives/16066</v>
-      </c>
-      <c r="AA12" t="str">
         <v>https://downloadgameps3.net/archives/16064</v>
       </c>
-      <c r="AB12" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AC12" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AD12" t="str">
+      <c r="P12" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="R12" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -937,24 +880,27 @@
         <v>imagenes/PS2/Don 2 The Game.jpg</v>
       </c>
       <c r="E13" t="str">
-        <v>No</v>
-      </c>
-      <c r="K13" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F13" t="str">
+        <v>No</v>
+      </c>
+      <c r="H13" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I13" t="str">
+        <v>https://1fichier.com/?f8xjcnix7v</v>
+      </c>
+      <c r="N13" t="str">
+        <v>https://downloadgameps3.net/archives/15461</v>
       </c>
       <c r="O13" t="str">
-        <v>https://1fichier.com/?f8xjcnix7v</v>
-      </c>
-      <c r="Z13" t="str">
-        <v>https://downloadgameps3.net/archives/15461</v>
-      </c>
-      <c r="AA13" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB13" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC13" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P13" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q13" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -972,21 +918,24 @@
         <v>imagenes/PS2/Street Cricket Champions 2.jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="K14" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="H14" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I14" t="str">
+        <v>https://1fichier.com/?k4zstitdsv</v>
+      </c>
+      <c r="N14" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O14" t="str">
-        <v>https://1fichier.com/?k4zstitdsv</v>
-      </c>
-      <c r="Z14" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA14" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB14" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P14" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1004,30 +953,27 @@
         <v>imagenes/PS2/FIFA 13.jpg</v>
       </c>
       <c r="E15" t="str">
-        <v>No</v>
-      </c>
-      <c r="K15" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F15" t="str">
+        <v>No</v>
+      </c>
+      <c r="H15" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N15" t="str">
+        <v>https://downloadgameps3.net/archives/16060</v>
+      </c>
+      <c r="O15" t="str">
+        <v>https://downloadgameps3.net/archives/16062</v>
       </c>
       <c r="P15" t="str">
-        <v>https://1fichier.com/?icte3aafoo</v>
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="Q15" t="str">
-        <v>https://1fichier.com/?tz6nh3ar9d</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>https://downloadgameps3.net/archives/16060</v>
-      </c>
-      <c r="AA15" t="str">
-        <v>https://downloadgameps3.net/archives/16062</v>
-      </c>
-      <c r="AB15" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AC15" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AD15" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="R15" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1045,33 +991,21 @@
         <v>imagenes/PS2/Pro Evolution Soccer 2013 [PES 2013].jpg</v>
       </c>
       <c r="E16" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F16" t="str">
         <v>Sí</v>
       </c>
-      <c r="G16" t="str">
-        <v>https://mega.nz/#!wjJmQBwa!G3eQnv3C2uU_UZ8o6PQ_4NYg7MBVGtWTtbi5ppOkXFA</v>
-      </c>
-      <c r="H16" t="str">
-        <v>https://mega.nz/#!lmZWFBab!jDstTqNEMdqN8LYtwxTIwK7NBPXvzyAWAHJLME8dM98</v>
-      </c>
-      <c r="L16" t="str">
-        <v>http://www.mediafire.com/file/c3nekov9p86pb6s/PES_2013_%255BNTSC%255D_%255BEs%252CFr%252CEn%252CPt%255D.part1.rar/file</v>
-      </c>
-      <c r="M16" t="str">
-        <v>http://www.mediafire.com/file/pxisp2ip6ox8cra/PES_2013_%255BNTSC%255D_%255BEs%252CFr%252CEn%252CPt%255D.part2.rar/file</v>
+      <c r="I16" t="str">
+        <v>https://1fichier.com/?1m7g300a54</v>
       </c>
       <c r="N16" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O16" t="str">
-        <v>https://1fichier.com/?1m7g300a54</v>
-      </c>
-      <c r="Z16" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA16" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB16" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P16" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1089,21 +1023,24 @@
         <v>imagenes/PS2/Major League Baseball 2K12.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="K17" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="H17" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I17" t="str">
+        <v>https://1fichier.com/?wreuq925rg</v>
+      </c>
+      <c r="N17" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O17" t="str">
-        <v>https://1fichier.com/?wreuq925rg</v>
-      </c>
-      <c r="Z17" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA17" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB17" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P17" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1121,30 +1058,27 @@
         <v>imagenes/PS2/The Unknown City Horror Begins Now Episode 1.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
-      </c>
-      <c r="L18" t="str">
-        <v>https://filecrypt.cc/Container/0937080F38.html</v>
-      </c>
-      <c r="M18" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F18" t="str">
+        <v>No</v>
+      </c>
+      <c r="I18" t="str">
+        <v>https://1fichier.com/?dcwc00omn6z8nwev86ed?&amp;af=795144</v>
+      </c>
+      <c r="N18" t="str">
+        <v>https://downloadgameps3.com/guide-download-game/</v>
       </c>
       <c r="O18" t="str">
-        <v>https://1fichier.com/?dcwc00omn6z8nwev86ed?&amp;af=795144</v>
-      </c>
-      <c r="Z18" t="str">
-        <v>https://downloadgameps3.com/guide-download-game/</v>
-      </c>
-      <c r="AA18" t="str">
         <v>https://downloadgameps3.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AB18" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AC18" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AD18" t="str">
+      <c r="P18" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="R18" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1162,21 +1096,24 @@
         <v>imagenes/PS2/Moujuutsukai to Oujisama Snow Bride.jpg</v>
       </c>
       <c r="E19" t="str">
-        <v>No</v>
-      </c>
-      <c r="K19" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F19" t="str">
+        <v>No</v>
+      </c>
+      <c r="H19" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I19" t="str">
+        <v>https://1fichier.com/?6fiii2e88o</v>
+      </c>
+      <c r="N19" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O19" t="str">
-        <v>https://1fichier.com/?6fiii2e88o</v>
-      </c>
-      <c r="Z19" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA19" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB19" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P19" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1194,21 +1131,24 @@
         <v>imagenes/PS2/RaOne The Game.jpg</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="K20" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F20" t="str">
+        <v>No</v>
+      </c>
+      <c r="H20" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I20" t="str">
+        <v>https://1fichier.com/?a0k7773ray</v>
+      </c>
+      <c r="N20" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="O20" t="str">
-        <v>https://1fichier.com/?a0k7773ray</v>
-      </c>
-      <c r="Z20" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AA20" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AB20" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="P20" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
@@ -1226,30 +1166,33 @@
         <v>imagenes/PS2/Cart Kings.jpg</v>
       </c>
       <c r="E21" t="str">
-        <v>No</v>
-      </c>
-      <c r="K21" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F21" t="str">
+        <v>No</v>
+      </c>
+      <c r="H21" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I21" t="str">
+        <v>https://1fichier.com/?0fv99n4qi3</v>
+      </c>
+      <c r="N21" t="str">
+        <v>https://downloadgameps3.net/archives/14410</v>
       </c>
       <c r="O21" t="str">
-        <v>https://1fichier.com/?0fv99n4qi3</v>
-      </c>
-      <c r="Z21" t="str">
-        <v>https://downloadgameps3.net/archives/14410</v>
-      </c>
-      <c r="AA21" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AB21" t="str">
-        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
-      </c>
-      <c r="AC21" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P21" t="str">
+        <v>https://dlpsgame.com/guide-jdownloader-2/</v>
+      </c>
+      <c r="Q21" t="str">
         <v>https://docs.google.com/spreadsheets/d/1yPcDW8H56iq56E_a7EiJoll5-z_sVO-ZYDIsK0JkTYU/edit?gid=0#gid=0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
 </worksheet>
 </file>